--- a/InfoMath/ExemplesClasse/Donnees_-_Exemples_notes_de_cours.xlsx
+++ b/InfoMath/ExemplesClasse/Donnees_-_Exemples_notes_de_cours.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cvmqc-my.sharepoint.com/personal/achasse_cvm_qc_ca/Documents/2026 B Session Automne/201-B11-VM/Notes de cours/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cegepGit\InfoMath\ExemplesClasse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="268" documentId="8_{F39F7078-E834-462E-840A-2EBF6544809C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24DCE41F-29F7-4A6C-822A-2017536888E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4746EAF9-FB4D-46CD-BE7E-CFD93D908B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Données" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="3" r:id="rId1"/>
+    <sheet name="Données" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Âge">Données!$B$2:$B$41</definedName>
@@ -28,6 +29,9 @@
     <definedName name="Temps">Données!$I$2:$I$41</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="57">
   <si>
     <t>Individu</t>
   </si>
@@ -81,13 +85,154 @@
   </si>
   <si>
     <t>D</t>
+  </si>
+  <si>
+    <t>Étiquettes de lignes</t>
+  </si>
+  <si>
+    <t>Total général</t>
+  </si>
+  <si>
+    <t>Pourcentage cumulé d'étudiant.es</t>
+  </si>
+  <si>
+    <t>Pourcentage d'étudiant.es</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Niveau de motivation</t>
+  </si>
+  <si>
+    <t>Source : Inconnue</t>
+  </si>
+  <si>
+    <t>Nombre d'étudiant.es</t>
+  </si>
+  <si>
+    <t>Remarque :  22,5 % des etudiants ont un niveau de motivation très bas.</t>
+  </si>
+  <si>
+    <t>Répartition de 40 étudiant.es selon son niveau de motivation, CVM,2023</t>
+  </si>
+  <si>
+    <t>Remarque: la grande majorité est droitière</t>
+  </si>
+  <si>
+    <t>Répartition de 40 étudiant.es selon la main principale, CVM, 2023</t>
+  </si>
+  <si>
+    <t>Source: Inconnue.</t>
+  </si>
+  <si>
+    <t>Droit</t>
+  </si>
+  <si>
+    <t>Gauche</t>
+  </si>
+  <si>
+    <t>Maximum=</t>
+  </si>
+  <si>
+    <t>Minimum=</t>
+  </si>
+  <si>
+    <t>Étendue=</t>
+  </si>
+  <si>
+    <t>Nombre de classe=</t>
+  </si>
+  <si>
+    <t>Ampitude Idéale=</t>
+  </si>
+  <si>
+    <t>Amplitude Choisi=</t>
+  </si>
+  <si>
+    <t>À faire pour EXAMs</t>
+  </si>
+  <si>
+    <t>65-69</t>
+  </si>
+  <si>
+    <t>70-74</t>
+  </si>
+  <si>
+    <t>75-79</t>
+  </si>
+  <si>
+    <t>80-84</t>
+  </si>
+  <si>
+    <t>85-89</t>
+  </si>
+  <si>
+    <t>90-94</t>
+  </si>
+  <si>
+    <t>95-100</t>
+  </si>
+  <si>
+    <t>Moyenne Générale</t>
+  </si>
+  <si>
+    <t>Pourcentage cumulée</t>
+  </si>
+  <si>
+    <t>[55-59[</t>
+  </si>
+  <si>
+    <t>[60-64[</t>
+  </si>
+  <si>
+    <t>Source: Inconnue</t>
+  </si>
+  <si>
+    <t>Remarque: Plus de 50% des étudiant.es ont eu plus de 70%</t>
+  </si>
+  <si>
+    <t>15-16</t>
+  </si>
+  <si>
+    <t>17-18</t>
+  </si>
+  <si>
+    <t>19-20</t>
+  </si>
+  <si>
+    <t>21-22</t>
+  </si>
+  <si>
+    <t>23-24</t>
+  </si>
+  <si>
+    <t>25-26</t>
+  </si>
+  <si>
+    <t>33-35</t>
+  </si>
+  <si>
+    <t>Âge des étudiant.es</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Remarque</t>
+  </si>
+  <si>
+    <t>Pourcentage Cumulé d'étudiant.es</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,16 +240,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -112,24 +285,319 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -142,8 +610,185 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lenovo" refreshedDate="46267.614073842589" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{26070C5E-C586-4908-A4FE-AD991B86057B}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="Q8:U18" sheet="Données"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Âge des étudiant.es" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Nombre d'étudiant.es" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="40"/>
+    </cacheField>
+    <cacheField name="Pourcentage d'étudiant.es" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5" maxValue="100"/>
+    </cacheField>
+    <cacheField name="Champ4" caption="Champ4" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Pourcentage Cumulé d'étudiant.es" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5" maxValue="100"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
+  <r>
+    <s v="15-16"/>
+    <n v="1"/>
+    <n v="2.5"/>
+    <m/>
+    <n v="2.5"/>
+  </r>
+  <r>
+    <s v="17-18"/>
+    <n v="16"/>
+    <n v="40"/>
+    <m/>
+    <n v="42.5"/>
+  </r>
+  <r>
+    <s v="19-20"/>
+    <n v="15"/>
+    <n v="37.5"/>
+    <m/>
+    <n v="80"/>
+  </r>
+  <r>
+    <s v="21-22"/>
+    <n v="3"/>
+    <n v="7.5"/>
+    <m/>
+    <n v="87.5"/>
+  </r>
+  <r>
+    <s v="23-24"/>
+    <n v="1"/>
+    <n v="2.5"/>
+    <m/>
+    <n v="90"/>
+  </r>
+  <r>
+    <s v="25-26"/>
+    <n v="3"/>
+    <n v="7.5"/>
+    <m/>
+    <n v="97.5"/>
+  </r>
+  <r>
+    <s v="33-35"/>
+    <n v="1"/>
+    <n v="2.5"/>
+    <m/>
+    <n v="100"/>
+  </r>
+  <r>
+    <s v="Total général"/>
+    <n v="40"/>
+    <n v="100"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="Source"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="Remarque"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C56B3081-A456-42EA-A1DB-D9A8A80CD09D}" name="Tableau croisé dynamique6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="5">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00D275F3-D5C2-458E-B85E-0BB135DC7964}" name="Tableau3" displayName="Tableau3" ref="K22:M25" totalsRowShown="0">
+  <autoFilter ref="K22:M25" xr:uid="{00D275F3-D5C2-458E-B85E-0BB135DC7964}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{E3C40644-8AE1-45C1-8D27-468E10525DD5}" name="Étiquettes de lignes"/>
+    <tableColumn id="2" xr3:uid="{572CB24C-1253-4E92-B65E-167B391256E2}" name="Nombre d'étudiant.es"/>
+    <tableColumn id="3" xr3:uid="{E3075F66-DBB0-4D12-B453-B89B04D58E78}" name="Pourcentage d'étudiant.es">
+      <calculatedColumnFormula>L23/$L$25 * 100</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C776DB4F-F158-429A-ACE6-9A1ED6EB23BA}" name="Tableau4" displayName="Tableau4" ref="K39:N49" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="K39:N49" xr:uid="{C776DB4F-F158-429A-ACE6-9A1ED6EB23BA}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{F2FB24E5-729A-4487-BA49-EBC8A5A580A0}" name="Moyenne Générale" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{AA856B57-6283-4604-B36C-EDC04437DC4C}" name="Nombre d'étudiant.es" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{1C17DF40-1F8A-4A08-90F9-A4F75815ACE4}" name="Pourcentage d'étudiant.es" dataDxfId="1">
+      <calculatedColumnFormula>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{BF6B51D0-8034-45E4-A1F2-0B1A74AB08F0}" name="Pourcentage cumulée" dataDxfId="0">
+      <calculatedColumnFormula>N39+Tableau4[[#This Row],[Pourcentage d''étudiant.es]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{43119C11-FDB0-4C20-BF77-59D053063196}" name="Tableau6" displayName="Tableau6" ref="Q8:R18" totalsRowShown="0">
+  <autoFilter ref="Q8:R18" xr:uid="{43119C11-FDB0-4C20-BF77-59D053063196}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{37CBC284-8FFD-47DC-A24D-5AC63DC4923A}" name="Âge des étudiant.es"/>
+    <tableColumn id="2" xr3:uid="{60FC77FA-96CC-46C0-B1F0-5FDDBFCC3753}" name="Nombre d'étudiant.es"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,23 +1053,128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CB53BB-F3F4-4A15-9416-A3628BE8ECDA}">
+  <dimension ref="A3:C20"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:V51"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.453125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="6.453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="6.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.26953125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.26953125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7265625" customWidth="1"/>
-    <col min="13" max="13" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="30.42578125" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,7 +1203,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -482,7 +1232,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -512,7 +1262,7 @@
         <v>6.91</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A41" si="0">A3+1</f>
         <v>3</v>
@@ -542,7 +1292,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -572,7 +1322,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -601,8 +1351,14 @@
       <c r="I6" s="1">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K6" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -631,8 +1387,12 @@
       <c r="I7" s="1">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -661,8 +1421,34 @@
       <c r="I8" s="1">
         <v>7.12</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>53</v>
+      </c>
+      <c r="R8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S8" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="T8" s="39"/>
+      <c r="U8" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="V8" s="39"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -691,8 +1477,36 @@
       <c r="I9" s="1">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K9" s="20">
+        <v>0</v>
+      </c>
+      <c r="L9" s="21">
+        <v>4</v>
+      </c>
+      <c r="M9" s="22">
+        <f t="shared" ref="M9:M15" si="1">L9/$L$15*100</f>
+        <v>10</v>
+      </c>
+      <c r="N9" s="23">
+        <f>+M9</f>
+        <v>10</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="V9" s="40"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -721,8 +1535,36 @@
       <c r="I10" s="1">
         <v>6.35</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K10" s="24">
+        <v>1</v>
+      </c>
+      <c r="L10" s="25">
+        <v>5</v>
+      </c>
+      <c r="M10" s="26">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+      <c r="N10" s="27">
+        <f>N9+M10</f>
+        <v>22.5</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>47</v>
+      </c>
+      <c r="R10">
+        <v>16</v>
+      </c>
+      <c r="S10" s="40">
+        <v>40</v>
+      </c>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40">
+        <v>42.5</v>
+      </c>
+      <c r="V10" s="40"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -751,8 +1593,36 @@
       <c r="I11" s="1">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K11" s="20">
+        <v>2</v>
+      </c>
+      <c r="L11" s="21">
+        <v>5</v>
+      </c>
+      <c r="M11" s="22">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+      <c r="N11" s="23">
+        <f t="shared" ref="N11:N14" si="2">N10+M11</f>
+        <v>35</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>48</v>
+      </c>
+      <c r="R11">
+        <v>15</v>
+      </c>
+      <c r="S11" s="40">
+        <v>37.5</v>
+      </c>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40">
+        <v>80</v>
+      </c>
+      <c r="V11" s="40"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -781,8 +1651,36 @@
       <c r="I12" s="1">
         <v>9.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K12" s="24">
+        <v>3</v>
+      </c>
+      <c r="L12" s="25">
+        <v>8</v>
+      </c>
+      <c r="M12" s="26">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N12" s="27">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>49</v>
+      </c>
+      <c r="R12">
+        <v>3</v>
+      </c>
+      <c r="S12" s="40">
+        <v>7.5</v>
+      </c>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40">
+        <v>87.5</v>
+      </c>
+      <c r="V12" s="40"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -811,8 +1709,36 @@
       <c r="I13" s="1">
         <v>7.04</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K13" s="20">
+        <v>4</v>
+      </c>
+      <c r="L13" s="21">
+        <v>12</v>
+      </c>
+      <c r="M13" s="22">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="N13" s="23">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>50</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40">
+        <v>90</v>
+      </c>
+      <c r="V13" s="40"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -841,8 +1767,36 @@
       <c r="I14" s="1">
         <v>6.98</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K14" s="24">
+        <v>5</v>
+      </c>
+      <c r="L14" s="25">
+        <v>6</v>
+      </c>
+      <c r="M14" s="26">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="N14" s="27">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>51</v>
+      </c>
+      <c r="R14">
+        <v>3</v>
+      </c>
+      <c r="S14" s="40">
+        <v>7.5</v>
+      </c>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40">
+        <v>97.5</v>
+      </c>
+      <c r="V14" s="40"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -871,8 +1825,33 @@
       <c r="I15" s="1">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="16">
+        <v>40</v>
+      </c>
+      <c r="M15" s="28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N15" s="29"/>
+      <c r="Q15" t="s">
+        <v>52</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40">
+        <v>100</v>
+      </c>
+      <c r="V15" s="40"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -901,8 +1880,26 @@
       <c r="I16" s="1">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K16" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="Q16" t="s">
+        <v>12</v>
+      </c>
+      <c r="R16">
+        <v>40</v>
+      </c>
+      <c r="S16" s="40">
+        <v>100</v>
+      </c>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -931,8 +1928,21 @@
       <c r="I17" s="1">
         <v>7.11</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K17" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="Q17" t="s">
+        <v>54</v>
+      </c>
+      <c r="S17" s="39"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="39"/>
+      <c r="V17" s="39"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -961,8 +1971,11 @@
       <c r="I18" s="1">
         <v>8.4499999999999993</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -992,7 +2005,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1021,8 +2034,21 @@
       <c r="I20" s="1">
         <v>7.94</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K20" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="30"/>
+      <c r="Q20" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="R20" s="32">
+        <f>MAX(Âge)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1051,12 +2077,21 @@
       <c r="I21" s="1">
         <v>7.62</v>
       </c>
-      <c r="L21" s="3"/>
-      <c r="N21" s="2"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="30"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q21" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="R21" s="32">
+        <f>MIN(Âge)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1084,12 +2119,28 @@
       </c>
       <c r="I22" s="1">
         <v>7.77</v>
+      </c>
+      <c r="K22" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" t="s">
+        <v>14</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q22" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="R22" s="32">
+        <f>R20-R21</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1118,8 +2169,24 @@
       <c r="I23" s="1">
         <v>6.05</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23">
+        <v>34</v>
+      </c>
+      <c r="M23">
+        <f>L23/$L$25 * 100</f>
+        <v>85</v>
+      </c>
+      <c r="Q23" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R23" s="33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1148,8 +2215,25 @@
       <c r="I24" s="1">
         <v>6.81</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24">
+        <v>6</v>
+      </c>
+      <c r="M24">
+        <f t="shared" ref="M24:M25" si="3">L24/$L$25 * 100</f>
+        <v>15</v>
+      </c>
+      <c r="Q24" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R24" s="32">
+        <f>R22/R23</f>
+        <v>2.7142857142857144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1178,8 +2262,24 @@
       <c r="I25" s="1">
         <v>6.83</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K25" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25">
+        <v>40</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="Q25" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="R25" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1208,8 +2308,13 @@
       <c r="I26" s="1">
         <v>7.12</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K26" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1239,8 +2344,13 @@
         <v>8.94</v>
       </c>
       <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K27" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1271,7 +2381,7 @@
       </c>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1302,7 +2412,7 @@
       </c>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1332,8 +2442,12 @@
         <v>7.59</v>
       </c>
       <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K30" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" s="39"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1363,8 +2477,15 @@
         <v>7.45</v>
       </c>
       <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K31" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31">
+        <f>MAX(Moy.générale)</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1394,8 +2515,15 @@
         <v>6.99</v>
       </c>
       <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K32" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32">
+        <f>MIN(Moy.générale)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1425,8 +2553,15 @@
         <v>6.7</v>
       </c>
       <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33">
+        <f>L31-L32</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1456,8 +2591,14 @@
         <v>6.75</v>
       </c>
       <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K34" t="s">
+        <v>29</v>
+      </c>
+      <c r="L34" s="31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -1487,8 +2628,15 @@
         <v>6.83</v>
       </c>
       <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K35" t="s">
+        <v>30</v>
+      </c>
+      <c r="L35">
+        <f>L33/L34</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -1517,8 +2665,14 @@
       <c r="I36" s="1">
         <v>9.02</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K36" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -1548,7 +2702,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -1578,7 +2732,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -1607,8 +2761,20 @@
       <c r="I39" s="1">
         <v>8.42</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K39" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L39" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N39" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -1637,8 +2803,21 @@
       <c r="I40" s="1">
         <v>8.0299999999999994</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K40" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L40" s="13">
+        <v>2</v>
+      </c>
+      <c r="M40" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>5</v>
+      </c>
+      <c r="N40" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -1667,9 +2846,199 @@
       <c r="I41" s="1">
         <v>7.41</v>
       </c>
+      <c r="K41" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L41" s="13">
+        <v>8</v>
+      </c>
+      <c r="M41" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>20</v>
+      </c>
+      <c r="N41" s="14">
+        <f>N40+Tableau4[[#This Row],[Pourcentage d''étudiant.es]]</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K42" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L42" s="13">
+        <v>8</v>
+      </c>
+      <c r="M42" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>20</v>
+      </c>
+      <c r="N42" s="14">
+        <f>N41+Tableau4[[#This Row],[Pourcentage d''étudiant.es]]</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K43" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43" s="13">
+        <v>5</v>
+      </c>
+      <c r="M43" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>12.5</v>
+      </c>
+      <c r="N43" s="14">
+        <f>N42+Tableau4[[#This Row],[Pourcentage d''étudiant.es]]</f>
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="L44" s="13">
+        <v>6</v>
+      </c>
+      <c r="M44" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>15</v>
+      </c>
+      <c r="N44" s="14">
+        <f>N43+Tableau4[[#This Row],[Pourcentage d''étudiant.es]]</f>
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K45" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" s="13">
+        <v>4</v>
+      </c>
+      <c r="M45" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>10</v>
+      </c>
+      <c r="N45" s="14">
+        <f>N44+Tableau4[[#This Row],[Pourcentage d''étudiant.es]]</f>
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K46" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="L46" s="13">
+        <v>4</v>
+      </c>
+      <c r="M46" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>10</v>
+      </c>
+      <c r="N46" s="14">
+        <f>N45+Tableau4[[#This Row],[Pourcentage d''étudiant.es]]</f>
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K47" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="13">
+        <v>2</v>
+      </c>
+      <c r="M47" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>5</v>
+      </c>
+      <c r="N47" s="14">
+        <f>N46+Tableau4[[#This Row],[Pourcentage d''étudiant.es]]</f>
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K48" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L48" s="13">
+        <v>1</v>
+      </c>
+      <c r="M48" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>2.5</v>
+      </c>
+      <c r="N48" s="14">
+        <f>N47+Tableau4[[#This Row],[Pourcentage d''étudiant.es]]</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K49" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L49" s="13">
+        <v>40</v>
+      </c>
+      <c r="M49" s="14">
+        <f>Tableau4[[#This Row],[Nombre d''étudiant.es]]/$L$49*100</f>
+        <v>100</v>
+      </c>
+      <c r="N49" s="14"/>
+    </row>
+    <row r="50" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K50" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="L50" s="37"/>
+      <c r="M50" s="37"/>
+      <c r="N50" s="37"/>
+    </row>
+    <row r="51" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K51" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="L51" s="37"/>
+      <c r="M51" s="37"/>
+      <c r="N51" s="37"/>
     </row>
   </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K50:N50"/>
+    <mergeCell ref="K51:N51"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="K6:N7"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="K20:M21"/>
+    <mergeCell ref="K26:M26"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+  <tableParts count="3">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>